--- a/Final_Result.xlsx
+++ b/Final_Result.xlsx
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2127,7 +2127,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Final_Result.xlsx — The six selected models only. Rebuilt 2026-08-29 from the result files on disk.</t>
+          <t>Final_Result.xlsx — The six selected models only. Rebuilt 2026-08-29 from the result files on disk; bbh refreshed 2026-09-07.</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>the newest slots, and the least filled</t>
+          <t>the newest slots — bbh and Emo filled, MMLU and DocVQA not</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite and gpt-5.6-luna were selected after bbh, MMLU and DocVQA had been run on the models they replaced. Emo is complete for both; bbh has Gemini in progress; MMLU and DocVQA are blank for both and need re-running. The superseded pair's numbers stay in Results.xlsx and are not carried into these slots.</t>
+          <t>gemini-3.5-flash-lite and gpt-5.6-luna were selected after bbh, MMLU and DocVQA had been run on the models they replaced. bbh is now complete for both, 20 of 20 tasks each, refreshed 2026-09-07; Emo is complete for both, with the effort caveat on gpt-5.6-luna in the Emo row; MMLU and DocVQA are blank for both and need re-running. The superseded pair’s numbers stay in Results.xlsx and are not carried into these slots.</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Tasks_benchmarks/bbh/BBH_*/results/*_bbh_overall.csv</t>
+          <t>Tasks_benchmarks/bbh/BBH_*/results/&lt;task&gt;/&lt;model&gt;_overall.csv</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Refreshed 2026-08-29 from the uniform rescore, scorer tag lenient_v2: every model scored by the same six-branch matcher out of bbh_eval_core.py. The sheet is now reproducible from one source, and the old strict-vs-lenient caveat no longer applies here.</t>
+          <t>Refreshed 2026-09-07 from the per-task CSVs, scorer tag lenient_v5 (uniform across all 10 slots): every model scored by the same matcher out of bbh_eval_core.py. Read the per-task files, NOT the slot-level BBH_*/results/*_bbh_overall.csv — the DeepInfra repair of 2026-08-30 re-ran only the affected tasks and overwrote Gemma’s roll-up with 5 tasks and Qwen’s with 13, understating them by 0.089 and 0.019.</t>
         </is>
       </c>
     </row>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>1 of 20 tasks — run in progress</t>
+          <t>20 of 20 tasks — complete</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>The selected Gemini has started on bbh. Only the tasks it has finished carry a value; Overall Score stays blank until all 20 are in.</t>
+          <t>BBH_Gemini_Flash3.5lite_OpenRouter, 4,833 rows, macro 0.9375, no_marker 0, empty 0. Run 2026-08-29 on the settled OpenRouter route (google/gemini-3.5-flash-lite). This column no longer belongs to the superseded gemini-2.5-flash, which keeps its own column here.</t>
         </is>
       </c>
     </row>
@@ -2276,56 +2276,56 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>blank — not yet run</t>
+          <t>20 of 20 tasks — complete</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>BBH_GPT_5.6_Luna has a runner but no results.</t>
+          <t>BBH_GPT_5.6_Luna, 4,833 rows, macro 0.9349, no_marker 0, empty 0. Run 2026-08-29 at reasoning_effort="low", the settled config. Its output cap is chosen rather than measured, and no task came back truncated at it.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Big Bench Hard</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Overall Score</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>macro-average over the 20 tasks</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Written only for a column with all 20, so the row stays comparable. Kimi has 10 tasks and a 10-task macro of 0.8938, which is deliberately not put in a row labelled 20.</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Qwen = Qwen/Qwen3.5-9B</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20 of 20 tasks — complete, 17 rows unusable</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BBH_Qwen, 4,833 rows, macro 0.9339. The DeepInfra repair of 2026-08-30 took 256 unusable rows down to 17 — 16 no_marker and 1 empty, all in dyck_languages, which is scored 0.696 with them counted as wrong. No other slot among the six has any.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>MMLU</t>
+          <t>Big Bench Hard</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>Overall Score</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>mmlu &lt;model&gt;_overall_results.csv</t>
+          <t>macro-average over the 20 tasks</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Matches the previous workbook.</t>
+          <t>Written only for a column with all 20 tasks, so the row stays comparable — a partial column keeps a blank rather than a macro over fewer tasks.</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2337,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>XAI · Deepseek</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>mmlu/gemma/gemma_overall_results.csv</t>
+          <t>mmlu &lt;model&gt;_overall_results.csv</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>8 of 13 subjects; the other five were never written.</t>
+          <t>Matches the previous workbook.</t>
         </is>
       </c>
     </row>
@@ -2359,61 +2359,61 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>mmlu/gemma/gemma_overall_results.csv</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>qwen_overall_results.csv exists but is empty.</t>
+          <t>8 of 13 subjects; the other five were never written.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>MMLU · DocVQA</t>
+          <t>MMLU</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>scoring</t>
+          <t>Qwen</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>still per-runner</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Only bbh has been moved onto one shared lenient matcher. Until MMLU and DocVQA follow, their columns are not guaranteed to be scored the same way as each other.</t>
+          <t>qwen_overall_results.csv exists but is empty.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>DocVQA</t>
+          <t>MMLU · DocVQA</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Qwen · Gemma</t>
+          <t>scoring</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
+          <t>still per-runner</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
+          <t>Only bbh has been moved onto one shared lenient matcher. Until MMLU and DocVQA follow, their columns are not guaranteed to be scored the same way as each other.</t>
         </is>
       </c>
     </row>
@@ -2425,39 +2425,39 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>Qwen · Gemma</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>qwen_DocVQA/ and gemma_DocVQA/ overall CSVs</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>No DocVQA run exists.</t>
+          <t>Gemma is the two halves recombined weighted by rows: (2320+2658)/(2500+2849).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Emo</t>
+          <t>DocVQA</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>XAI · Deepseek</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
+          <t>No DocVQA run exists.</t>
         </is>
       </c>
     </row>
@@ -2469,17 +2469,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
+          <t>EMO_Gemini_Flash3.5lite_OpenRouter/results/{EU,EA}</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
+          <t>gemini-3.5-flash-lite on OpenRouter at reasoning effort minimal — the settled config.</t>
         </is>
       </c>
     </row>
@@ -2491,37 +2491,59 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>XAI · Qwen · Gemma · Deepseek</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>EmoBench/emobench_results.csv</t>
+          <t>EMO_GPT_5.6_Luna/results_default/{EU,EA}</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Unchanged.</t>
+          <t>gpt-5.6-luna at the default medium effort. The settled effort is low, and results_eLow has EU (0.650) but no EA, so no complete EmoBench score exists at the settled config. One EA run at effort=low closes it.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>Emo</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>XAI · Qwen · Gemma · Deepseek</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>EmoBench/emobench_results.csv</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>Awareness</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>every column</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>No model has been scored yet; awareness_results.csv holds only the paper baselines.</t>
         </is>

--- a/Final_Result.xlsx
+++ b/Final_Result.xlsx
@@ -1176,10 +1176,15 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="2" t="n">
+        <v>0.8</v>
+      </c>
       <c r="D3" s="2" t="n">
         <v>0.82</v>
       </c>
+      <c r="E3" t="n">
+        <v>0.83</v>
+      </c>
       <c r="F3" s="2" t="n">
         <v>0.82</v>
       </c>
@@ -1194,15 +1199,20 @@
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="n">
+        <v>0.8333</v>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8509</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.842</v>
+        <v>0.8421</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.904</v>
+        <v>0.9035</v>
       </c>
     </row>
     <row r="5">
@@ -1212,15 +1222,20 @@
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="n">
+        <v>0.9841</v>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>0.979</v>
+        <v>0.9788</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9788</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.984</v>
+        <v>0.9841</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.981</v>
+        <v>0.9815</v>
       </c>
     </row>
     <row r="6">
@@ -1230,12 +1245,20 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="2" t="n">
+        <v>0.9683</v>
+      </c>
       <c r="D6" s="2" t="n">
-        <v>0.976</v>
+        <v>0.9762</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9365</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9762</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.976</v>
+        <v>0.9762</v>
       </c>
     </row>
     <row r="7">
@@ -1245,15 +1268,20 @@
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
+      <c r="C7" s="2" t="n">
+        <v>0.9258999999999999</v>
+      </c>
       <c r="D7" s="2" t="n">
-        <v>0.898</v>
+        <v>0.8981</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8704</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.88</v>
+        <v>0.8796</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.889</v>
+        <v>0.8889</v>
       </c>
     </row>
     <row r="8">
@@ -1263,15 +1291,20 @@
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
+      <c r="C8" s="2" t="n">
+        <v>0.9202</v>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>0.902</v>
+        <v>0.9018</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8895999999999999</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.902</v>
+        <v>0.9018</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.902</v>
+        <v>0.9018</v>
       </c>
     </row>
     <row r="9">
@@ -1281,15 +1314,20 @@
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2" t="n">
+        <v>0.9223</v>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>0.903</v>
+        <v>0.9029</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9126</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.913</v>
+        <v>0.9126</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.903</v>
+        <v>0.9029</v>
       </c>
     </row>
     <row r="10">
@@ -1299,15 +1337,20 @@
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="n">
+        <v>0.9658</v>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9402</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9359</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.953</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.97</v>
+        <v>0.9701</v>
       </c>
     </row>
     <row r="11">
@@ -1317,12 +1360,20 @@
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
+      <c r="C11" s="2" t="n">
+        <v>0.9745</v>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>0.968</v>
+        <v>0.9681</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.963</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.958</v>
+        <v>0.9579</v>
       </c>
     </row>
     <row r="12">
@@ -1332,15 +1383,20 @@
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
+      <c r="C12" s="2" t="n">
+        <v>0.8728</v>
+      </c>
       <c r="D12" s="2" t="n">
-        <v>0.855</v>
+        <v>0.8555</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8121</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.835</v>
+        <v>0.8353</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.855</v>
+        <v>0.8555</v>
       </c>
     </row>
     <row r="13">
@@ -1350,12 +1406,20 @@
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
+      <c r="C13" s="2" t="n">
+        <v>0.8838</v>
+      </c>
       <c r="D13" s="2" t="n">
-        <v>0.849</v>
+        <v>0.8492</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7609</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8715000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.869</v>
+        <v>0.8693</v>
       </c>
     </row>
     <row r="14">
@@ -1365,10 +1429,18 @@
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
+      <c r="C14" s="2" t="n">
+        <v>0.9164</v>
+      </c>
       <c r="D14" s="2" t="n">
         <v>0.881</v>
       </c>
+      <c r="E14" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8778</v>
+      </c>
       <c r="G14" s="2" t="n">
         <v>0.91</v>
       </c>
@@ -1380,12 +1452,20 @@
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
+      <c r="C15" s="2" t="n">
+        <v>0.961</v>
+      </c>
       <c r="D15" s="2" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9362</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9113</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9752</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.979</v>
+        <v>0.9787</v>
       </c>
     </row>
     <row r="16">
@@ -1395,12 +1475,18 @@
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="n">
+        <v>0.9176</v>
+      </c>
       <c r="D16" s="4" t="n">
         <v>0.9018</v>
       </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
+      <c r="E16" s="3" t="n">
+        <v>0.8802</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.9071</v>
+      </c>
       <c r="G16" s="4" t="n">
         <v>0.9174</v>
       </c>
@@ -2210,12 +2296,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>the newest slots — bbh and Emo filled, MMLU and DocVQA not</t>
+          <t>the newest slots — bbh and Emo filled, MMLU half, DocVQA not</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite and gpt-5.6-luna were selected after bbh, MMLU and DocVQA had been run on the models they replaced. bbh is now complete for both, 20 of 20 tasks each, refreshed 2026-09-07; Emo is complete for both, with the effort caveat on gpt-5.6-luna in the Emo row; MMLU and DocVQA are blank for both and need re-running. The superseded pair’s numbers stay in Results.xlsx and are not carried into these slots.</t>
+          <t>gemini-3.5-flash-lite and gpt-5.6-luna were selected after bbh, MMLU and DocVQA had been run on the models they replaced. bbh is complete for both, 20 of 20 tasks each; Emo is complete for both, with the effort caveat on gpt-5.6-luna in the Emo row; on MMLU gpt-5.6-luna is complete and gemini-3.5-flash-lite is deliberately blank (see the MMLU row); DocVQA is blank for both and needs re-running. The superseded pair’s numbers stay in Results.xlsx and are not carried into these slots.</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2423,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>XAI · Deepseek</t>
+          <t>every column</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>mmlu &lt;model&gt;_overall_results.csv</t>
+          <t>Tasks_benchmarks/mmlu/MMLU_*/&lt;vendor&gt;_&lt;Subject&gt;.csv, and MMLU_*/results/&lt;Subject&gt;/&lt;slug&gt;_overall.csv for the two newest slots</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Matches the previous workbook.</t>
+          <t>Refreshed 2026-09-07 from the per-subject files. Every column that has rows has all 13 subjects and 3,943 items. The &lt;vendor&gt;_overall_results.csv roll-ups are NOT the source: Gemma's covers 8 subjects and Qwen's is an empty file, while both have all 13 on disk — the same trap bbh's slot-level roll-up carries.</t>
         </is>
       </c>
     </row>
@@ -2359,17 +2445,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Gemini — blank here</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>mmlu/gemma/gemma_overall_results.csv</t>
+          <t>kept out by the user's decision, 2026-09-07</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>8 of 13 subjects; the other five were never written.</t>
+          <t>The run is complete (macro 0.9135) but its 3,943 rows are two routes, so it is recorded in Results.xlsx as a model result and not carried into the reported six. The column stays blank until a single-route run exists.</t>
         </is>
       </c>
     </row>
@@ -2381,17 +2467,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Qwen</t>
+          <t>OpenAI = gpt-5.6-luna</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>13 of 13 subjects</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>qwen_overall_results.csv exists but is empty.</t>
+          <t>MMLU_GPT_5.6_Luna, 3,943 rows, macro 0.9176, 0 empty, 0 no_marker. One route, reasoning_effort=low, the settled config. Run 2026-08-30 as a 5-shard array, merged 2026-09-07.</t>
         </is>
       </c>
     </row>
@@ -2408,12 +2494,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>still per-runner</t>
+          <t>two scorers on MMLU</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Only bbh has been moved onto one shared lenient matcher. Until MMLU and DocVQA follow, their columns are not guaranteed to be scored the same way as each other.</t>
+          <t>Two scorers behind this sheet. OpenAI is scored by mmlu_eval_core.score_response (mmlu_lenient_v1), the one lenient matcher; XAI, Qwen, Gemma and Deepseek carry the score their own runner wrote with ==. A uniform rescore of those four has not been run, so a small difference between them and the OpenAI column may be the scorer rather than the model. DocVQA is still per-runner throughout.</t>
         </is>
       </c>
     </row>
